--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185279</v>
       </c>
       <c r="B2" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185279</v>
       </c>
       <c r="B2" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185279</v>
       </c>
       <c r="B2" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185279</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185279</v>
       </c>
       <c r="B2" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185279</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185279</v>
       </c>
       <c r="B2" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128185279</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>92818</v>
+        <v>93137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,11 @@
           <t>Aivars Dunskis</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93137</v>
+        <v>93139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93139</v>
+        <v>93140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93140</v>
+        <v>93141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93141</v>
+        <v>93144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93144</v>
+        <v>93145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93145</v>
+        <v>93151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93151</v>
+        <v>93152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38968-2025 artfynd.xlsx
+++ b/artfynd/A 38968-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>128185287</v>
       </c>
       <c r="B3" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
